--- a/data/argentina/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/argentina/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,491 +448,491 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SvlzcWFD</t>
+          <t>On7sciXA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>65Xumenk</t>
+          <t>vJHhFDVs</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8fN0daP2</t>
+          <t>QZF0Di0f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jJjztvuM</t>
+          <t>8b55CBF0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>rDFDgc9L</t>
+          <t>WY1N1FIu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>U9kvubfS</t>
+          <t>nqHdEXpl</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>xzFHhHOR</t>
+          <t>AP0R0ZXo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bPuAZyIk</t>
+          <t>4n0Vagmh</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tlVEYeXe</t>
+          <t>pd8wbXH4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KvUIXFn2</t>
+          <t>M199BVU6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>U9B9fwfF</t>
+          <t>fF7H99aJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vq1qlyXr</t>
+          <t>xAVQJgNQ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>nkx6zI2q</t>
+          <t>GO8DAkpD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>pdWqnF1e</t>
+          <t>2XIYbD2b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>noM4eJv9</t>
+          <t>trxILFhE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>xCbnCYTO</t>
+          <t>nPhF1f1r</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>4M6ZEzp6</t>
+          <t>hMZipgW7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>IPW8TZba</t>
+          <t>vJVmoZG1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>2.80</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bLarDEEI</t>
+          <t>fRDz9x98</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>SzvdWyFt</t>
+          <t>WCfRbho1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>W88RGdFg</t>
+          <t>2iHr7GwL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>GIoEQXrI</t>
+          <t>badJ0EGl</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>4bOnOvNJ</t>
+          <t>trGn6zgR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -942,46 +942,46 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>zsFIIIps</t>
+          <t>hMeNaYVf</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>EXDMHx0m</t>
+          <t>llkWcC07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -991,227 +991,931 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>dGVCSgE5</t>
+          <t>YHCv8dOE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>GdAwEfaC</t>
+          <t>fotMKZ7K</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>QRiUzI6P</t>
+          <t>KtcNbhUl</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>xSnARDTB</t>
+          <t>YFg0qDU1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>AaT0VeUn</t>
+          <t>KIEz8d72</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>O2X4UFqg</t>
+          <t>lb6i4E6R</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2gp4aepJ</t>
+          <t>hWlzdjE7</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>I1SjNbxQ</t>
+          <t>j7hJaYEr</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>2.88</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Aa7VFGUa</t>
+          <t>6ZGn5fiL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>ngdGLTFj</t>
+          <t>61wK3sGG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>nailnFpq</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>hWCr6zxF</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>byzC53o4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>bXeRcCqe</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>6ZxIKZj8</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>pQyMJg6E</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>SAvG4N0A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>02ehoZak</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>fPfdpgFe</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>b9Dv7GM8</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>tdoWdWb1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>E7EtjOoH</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Qora851o</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>bBOHeSHu</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>lxFheb6a</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>SSDdfIL5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>WKADjzLU</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>xMo37PGi</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>pSMPg6nh</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>6sBYipH4</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>Kpy86qWc</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>KpFxi4WA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>OILThQ1b</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>CrfHqMOp</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>IH69iG5O</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>AZ7kl2GT</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>x2NLfnXo</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>Of75hdjI</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>p481gxyC</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>hbDpkr1N</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>fgvPVMI8</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>Y9EiyTMr</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2.80</t>
         </is>
       </c>
     </row>
